--- a/outputs/monitor_xlsx/20260123.xlsx
+++ b/outputs/monitor_xlsx/20260123.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1190,12 +1188,7 @@
       <c r="N4" t="n">
         <v>0.11</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1236,12 +1229,7 @@
       <c r="M5" t="n">
         <v>-20598</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1294,12 +1282,7 @@
       <c r="N6" t="n">
         <v>2.22</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1352,12 +1335,7 @@
       <c r="N7" t="n">
         <v>-5.75</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1410,12 +1388,7 @@
       <c r="N8" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1468,12 +1441,7 @@
       <c r="N9" t="n">
         <v>0.85</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1526,12 +1494,7 @@
       <c r="N10" t="n">
         <v>-5.68</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1584,12 +1547,7 @@
       <c r="N11" t="n">
         <v>11.94</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1642,12 +1600,7 @@
       <c r="N12" t="n">
         <v>2.79</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1700,12 +1653,7 @@
       <c r="N13" t="n">
         <v>2.34</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1758,12 +1706,7 @@
       <c r="N14" t="n">
         <v>7.45</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1816,12 +1759,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1874,12 +1812,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1932,12 +1865,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1987,12 +1915,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2045,12 +1968,7 @@
       <c r="N19" t="n">
         <v>5.31</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2103,11 +2021,6 @@
       <c r="N20" t="n">
         <v>-18.67</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2156,11 +2069,6 @@
       <c r="N21" t="n">
         <v>4.13</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2209,11 +2117,6 @@
       <c r="N22" t="n">
         <v>-7.77</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2262,11 +2165,6 @@
       <c r="N23" t="n">
         <v>-1.22</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2315,11 +2213,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2367,11 +2260,6 @@
       </c>
       <c r="N25" t="n">
         <v>2.72</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260123.xlsx
+++ b/outputs/monitor_xlsx/20260123.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,41 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>72.25</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.63</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>70983</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="G4" t="n">
-        <v>-143552</v>
+      <c r="H4" t="n">
+        <v>-142411</v>
       </c>
       <c r="I4" t="n">
-        <v>-5007</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
+        <v>-8257</v>
+      </c>
+      <c r="K4" t="n">
         <v>19710</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>7375</v>
       </c>
-      <c r="L4" t="n">
-        <v>38831</v>
-      </c>
       <c r="M4" t="n">
+        <v>38703</v>
+      </c>
+      <c r="N4" t="n">
         <v>-3945746</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.11</v>
+      <c r="O4" t="n">
+        <v>1.34</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1246,41 +1251,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>1030</v>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="E6" s="7" t="n">
         <v>-4.63</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="6" t="n">
         <v>5006</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>-169</v>
       </c>
-      <c r="G6" t="n">
-        <v>798</v>
-      </c>
       <c r="H6" t="n">
+        <v>667</v>
+      </c>
+      <c r="I6" t="n">
         <v>-184</v>
       </c>
-      <c r="I6" t="n">
-        <v>818</v>
-      </c>
       <c r="J6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K6" t="n">
         <v>235</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2893</v>
       </c>
-      <c r="L6" t="n">
-        <v>15451</v>
-      </c>
       <c r="M6" t="n">
+        <v>15031</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78600</v>
       </c>
-      <c r="N6" t="n">
-        <v>2.22</v>
+      <c r="O6" t="n">
+        <v>12.18</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1352,41 +1362,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1260</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="6" t="n">
         <v>18187</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>-1424</v>
       </c>
-      <c r="G8" t="n">
-        <v>10795</v>
-      </c>
       <c r="H8" t="n">
+        <v>3149</v>
+      </c>
+      <c r="I8" t="n">
         <v>203</v>
       </c>
-      <c r="I8" t="n">
-        <v>776</v>
-      </c>
       <c r="J8" t="n">
+        <v>802</v>
+      </c>
+      <c r="K8" t="n">
         <v>345</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>8847</v>
       </c>
-      <c r="L8" t="n">
-        <v>43137</v>
-      </c>
       <c r="M8" t="n">
+        <v>43181</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648461</v>
       </c>
-      <c r="N8" t="n">
-        <v>9.470000000000001</v>
+      <c r="O8" t="n">
+        <v>14.29</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1405,41 +1420,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1770</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>0.57</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="6" t="n">
         <v>29676</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="G9" s="6" t="n">
         <v>-4918</v>
       </c>
-      <c r="G9" t="n">
-        <v>-26688</v>
-      </c>
       <c r="H9" t="n">
+        <v>-41711</v>
+      </c>
+      <c r="I9" t="n">
         <v>3364</v>
       </c>
-      <c r="I9" t="n">
-        <v>-4090</v>
-      </c>
       <c r="J9" t="n">
+        <v>-934</v>
+      </c>
+      <c r="K9" t="n">
         <v>373</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>20681</v>
       </c>
-      <c r="L9" t="n">
-        <v>104831</v>
-      </c>
       <c r="M9" t="n">
+        <v>104920</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482794</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.85</v>
+      <c r="O9" t="n">
+        <v>2.56</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1511,41 +1531,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>1800</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>8.43</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>6140</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>1454</v>
       </c>
-      <c r="G11" t="n">
-        <v>3900</v>
-      </c>
       <c r="H11" t="n">
+        <v>5177</v>
+      </c>
+      <c r="I11" t="n">
         <v>8</v>
       </c>
-      <c r="I11" t="n">
-        <v>-1255</v>
-      </c>
       <c r="J11" t="n">
+        <v>-1151</v>
+      </c>
+      <c r="K11" t="n">
         <v>272</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>2254</v>
       </c>
-      <c r="L11" t="n">
-        <v>12082</v>
-      </c>
       <c r="M11" t="n">
+        <v>11575</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89462</v>
       </c>
-      <c r="N11" t="n">
-        <v>11.94</v>
+      <c r="O11" t="n">
+        <v>11.14</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1670,41 +1695,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1355</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>4.63</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>4939</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>720</v>
       </c>
-      <c r="G14" t="n">
-        <v>-230</v>
-      </c>
       <c r="H14" t="n">
+        <v>680</v>
+      </c>
+      <c r="I14" t="n">
         <v>225</v>
       </c>
-      <c r="I14" t="n">
-        <v>-70</v>
-      </c>
       <c r="J14" t="n">
+        <v>302</v>
+      </c>
+      <c r="K14" t="n">
         <v>75</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>4958</v>
       </c>
-      <c r="L14" t="n">
-        <v>26165</v>
-      </c>
       <c r="M14" t="n">
+        <v>25765</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19170</v>
       </c>
-      <c r="N14" t="n">
-        <v>7.45</v>
+      <c r="O14" t="n">
+        <v>2.75</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1723,42 +1753,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1095</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>800</v>
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>423</v>
       </c>
-      <c r="G15" t="n">
-        <v>970</v>
-      </c>
       <c r="H15" t="n">
+        <v>1656</v>
+      </c>
+      <c r="I15" t="n">
         <v>69</v>
       </c>
-      <c r="I15" t="n">
-        <v>953</v>
-      </c>
       <c r="J15" t="n">
+        <v>1022</v>
+      </c>
+      <c r="K15" t="n">
         <v>-16</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-249</v>
       </c>
-      <c r="L15" t="n">
-        <v>-424</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-753</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1882,39 +1917,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>338.5</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6.28</v>
-      </c>
-      <c r="E18" t="n">
-        <v>36878</v>
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="6" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>-1280</v>
       </c>
-      <c r="G18" t="n">
-        <v>-5847</v>
+      <c r="H18" t="n">
+        <v>-5684</v>
       </c>
       <c r="I18" t="n">
-        <v>2780</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>3009</v>
+      </c>
+      <c r="K18" t="n">
         <v>-15</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>501</v>
       </c>
-      <c r="L18" t="n">
-        <v>-636</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-78</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2129,41 +2172,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1175</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>2.17</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>4301</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>284</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>1272</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-309</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-1924</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>57</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2580</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>12814</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140155</v>
       </c>
-      <c r="N23" t="n">
-        <v>-1.22</v>
+      <c r="O23" t="n">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="24">
@@ -2177,42 +2225,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="6" t="n">
         <v>-4</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-106</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-20</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-15</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>-164</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2260,6 +2313,218 @@
       </c>
       <c r="N25" t="n">
         <v>2.72</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>1811</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2168</v>
+      </c>
+      <c r="I26" t="n">
+        <v>40</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-922</v>
+      </c>
+      <c r="K26" t="n">
+        <v>56</v>
+      </c>
+      <c r="L26" t="n">
+        <v>924</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4471</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-106258</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>3905</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>534</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>114</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I27" t="n">
+        <v>57</v>
+      </c>
+      <c r="J27" t="n">
+        <v>274</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>356</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2006</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8862</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9.630000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>319</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1743</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-195</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>228</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>5843</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>817</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15</v>
+      </c>
+      <c r="I29" t="n">
+        <v>189</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-138</v>
+      </c>
+      <c r="K29" t="n">
+        <v>50</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6499</v>
+      </c>
+      <c r="M29" t="n">
+        <v>33175</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21425</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
